--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T13:28:20+00:00</t>
+    <t>2024-10-24T09:42:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T09:42:16+00:00</t>
+    <t>2024-10-24T11:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-TRE-R221-ModeleDocumentCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T11:31:22+00:00</t>
+    <t>2024-10-29T18:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
